--- a/F3M_FP&A_assessment_ready_AI_v1.xlsx
+++ b/F3M_FP&A_assessment_ready_AI_v1.xlsx
@@ -1870,15 +1870,9 @@
       <c r="H2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="1">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1">
-        <v>4</v>
-      </c>
-      <c r="K2" s="1">
-        <v>3</v>
-      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="1">
         <f t="shared" ref="L2:L21" si="0">IF(COUNTA(I2:K2)=0,"",ROUND(AVERAGE(I2:K2),2))</f>
         <v>3</v>
